--- a/job_applications.xlsx
+++ b/job_applications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -518,9 +518,39 @@
         <v>30/9/2025, 2:49:47 am</v>
       </c>
     </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>Harsh Jajaniya</v>
+      </c>
+      <c r="B5" t="str">
+        <v>harsh@gmail.com</v>
+      </c>
+      <c r="C5" t="str" xml:space="preserve">
+        <v xml:space="preserve">07500327380
+</v>
+      </c>
+      <c r="D5" t="str">
+        <v>MMIL</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Btech</v>
+      </c>
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>8</v>
+      </c>
+      <c r="I5" t="str">
+        <v>CTC</v>
+      </c>
+      <c r="J5" t="str">
+        <v>1/6/2026, 6:21:37 PM</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>